--- a/docs/triton-learning/cards/triton-lesson-07-extern-functions-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-07-extern-functions-oral.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -36,54 +36,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：Triton 3.7.1 的 kernel 里一行 y = libdevice.asin(x)，x 是 fp32 的块，目标是 NVIDIA 后端。从 Python 到 PTX 依次经过哪些环节，每一环谁负责、产出什么，最后为什么 GPU 上没有函数调用？</t>
+          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：给一个非 NVIDIA 的 Triton 3.7.1 后端接入 libdevice，后端要往编译流程的哪几环填自己的内容？每一环漏掉或写错时，会在哪里、以什么现象失败？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：前端只记下要调用哪个符号，函数体到 LLVM IR 阶段才从厂商库链接进来并内联，所以运行时只剩普通指令。
-• [T#B#前端]：libdevice 是接口模块，翻译成 TTIR 时按后端换成实现模块；实现按参数 dtype 查表得到符号 __nv_asinf，TTIR 里记下一条带符号名的逐元素操作。
-• [T#B#布局与降级]：TTGIR 的布局决定每个线程持有 E 个元素；降级到 LLVM IR 时，Triton 替一个线程写程序：1 条声明，E 次标量调用。
-• [T#B#链接与内联]：后端发现有未定义的函数，就按名字从 libdevice 的 bitcode 里只拷入这一份定义；O3 把 E 次调用内联成 E 份函数体，定义被删除。
-• [T#B#数值模式]：生成 PTX 时，反射参数把库里的编译期分支折叠成一种写法，默认是冲掉次正规数、近似 sqrt。
-[T#B,!c47f17#边界]：代价有三处：半精度输入查不到表，必须先转 fp32；代码量随 E 增长；默认的数值模式偏快，要和 eager 对齐得主动调整。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：按名字链接、内联这些机制是 Triton 的公共代码；后端按流水线往四环里填内容：前端的映射与符号表、库文件、链接、内联。每一环漏掉都有固定的现象。
+• [T#B#前端]：get_module_map() 把接口模块映射到自己的实现模块，没生效时空壳函数返回 None，报错落在下一行的 tl.store；实现里缺函数报 AttributeError；dtype 不在符号表里报 KeyError。
+• [T#B#库与缓存键]：提供库文件和默认路径；NVIDIA 把库的内容哈希计入缓存键，所以换库会重新编译，路径写错则在算缓存键时就报 FileNotFoundError。
+• [T#B#链接]：链接发生在 LLVM IR 上，表里的符号名要和库里的定义同名；缺库或对不上时链接本身不报错，到最后一步才报找不到定义。
+• [T#B#内联]：库函数要被内联，否则机器码里留下真实调用；看链接后的 IR：有 define 是没内联，只有 declare 是没链接。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明接口模块按后端替换，并按 dtype 查表得到符号；说明布局决定每线程 E 个元素，LLVM IR 里是 1 条声明和 E 次调用；说明按名字只链接用到的定义，O3 内联后没有 call；说明反射参数在生成 PTX 时选定默认的数值模式；至少说出一个代价：半精度要先转、代码量随 E 增长或默认偏快</t>
+          <t xml:space="preserve">前端三项：映射没生效时返回 None、下一行才报错；缺函数报 AttributeError；dtype 缺项报 KeyError；库文件与缓存键：内容哈希进缓存键，路径错误最早报 FileNotFoundError；链接：符号名要和库里的定义一致，否则到最后一步才报错；内联：用链接后的 IR 区分没内联（define）和没链接（declare）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 全链路串联</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 四条实现路线与后端迁移</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒回答面试官：一个用 Triton 写的或由 PyTorch Inductor 生成的 kernel，结果和 PyTorch eager 相比在个别元素上不一致，有的差最后一两位，有的在极小的数上一个得 0、一个不是 0。可能的来源有哪些，你会按什么顺序排查和对齐？</t>
+          <t xml:space="preserve">请用约 60–90 秒向面试官说明：在 Triton 3.7.1 的 kernel 里算一个数学函数，可以用 tl.math、libdevice、tl.inline_asm_elementwise，或用 extern_libs 传入自己的库。你会看哪几个方面、怎样在这四条路线之间选择？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先看有没有用快速档的运算，再看次正规数的处理，最后看用的是哪一份数学库；三者都能通过写法或编译选项对齐。
-• [T#B#快速档]：tl.exp、tl.sqrt 和普通除法都是近似实现，差最后一两位先查这里，换成 libdevice.exp、tl.sqrt_rn、tl.div_rn。
-• [T#B#次正规数]：只在极小的数上不一致，多半是 libdevice 默认把次正规数冲成 0；启动时传 enable_reflect_ftz=False。
-• [T#B#库的差异]：不同的数学库用不同的多项式，同一个函数会差最后一位；可以把 Triton 自带的 libdevice 换成 CUDA 工具链的那一份。
-• [T#B#Inductor]：PyTorch 2.13 的 Inductor 把这三件事做成了 eager_numerics 的开关，默认已经选了精确的 sqrt 和 exp。
-[T#B,!c47f17#边界]：对齐有代价，精确档更慢，先确认业务是否真的需要逐位一致。跨后端时默认值还可能相反，例如 AMD 默认保留次正规数。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：默认用后端中立的 tl.math；它没有的函数用 libdevice；厂商库也没有时，自己提供库并经 extern_libs 传入；只有确实需要某条指令、又只面向一个后端时，才写内联汇编。
+• [T#B#可移植性]：tl.math 只说要算什么，实现由各后端决定；libdevice 点名厂商库里的函数，函数多得多，但要确认目标后端实现了它；内联汇编的文本原样进最终汇编，换后端就报 invalid instruction。
+• [T#B#精度与代价]：tl.exp、tl.sqrt、a / b 都是快速档；要和 eager 对齐就换成 libdevice.exp、tl.sqrt_rn、tl.div_rn，代价是更慢。
+• [T#B#dtype]：libdevice 和 tl.math 的超越函数都只收 fp32、fp64，半精度输入要先在 kernel 里转成 fp32。
+• [T#B#扩展]：自己提供的库要配一张 dtype 到符号的表，之后走和 libdevice 完全相同的链接与内联。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">区分三类来源：近似指令、次正规数处理、数学库的差异；说出 exp、sqrt、除法各自的精确写法；说出 enable_reflect_ftz 的作用和影响范围；说明对齐有性能代价，并先确认是否需要逐位一致</t>
+          <t xml:space="preserve">给出选择顺序：tl.math → libdevice → 自己提供的库；内联汇编只在单一后端、需要特定指令时用；可移植性：tl.math 后端中立，libdevice 要目标后端实现该函数，内联汇编绑定一种指令集；精度与代价：说出快速档对应的精确写法，并说明精确档更慢；dtype：两条库路线只收 fp32、fp64，半精度要先转；扩展：自己提供的库走和 libdevice 相同的链接与内联</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 数值对齐串联</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 四条实现路线与后端迁移</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：Triton 3.7.1 的 kernel 里一行 y = libdevice.asin(x)，x 是 fp32 的块，目标是 NVIDIA 后端。从 Python 到 PTX 依次经过哪些环节，每一环由谁负责、产出什么？为什么最后 GPU 上没有函数调用？</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：前端只记下要调用哪个符号；Triton 一直降级到 LLVM IR，函数体这时才由后端从厂商库链接进来、经 O3 内联，所以 GPU 上只剩普通指令。
+• [T#B#前端]：libdevice 是接口模块，翻译成 TTIR 时按后端换成实现模块；实现按参数 dtype 查表得到 __nv_asinf，TTIR 里记下一条带符号名的逐元素操作。
+• [T#B#Triton 降级]：TTGIR 的布局决定每个线程持有 E 个元素；Triton 降级到 LLVM IR 时替一个线程写程序：1 条声明，E 次标量调用。
+• [T#B#LLVM 阶段]：后端调用 LLVM，按名字从 libdevice 的 bitcode 里只拷入这一份定义；O3 把 E 次调用内联成 E 份函数体，定义被删除。
+• [T#B#生成 PTX]：反射参数把库里的编译期分支折叠成一种写法，默认是清零次正规数、近似 sqrt。
+• [T#B#延伸]：代价有三处：半精度输入要先转 fp32；代码量随 E 增长；默认数值模式偏快，要和 eager 对齐得主动调整。</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明接口模块按后端替换，并按 dtype 查表得到符号；说明布局决定每线程 E 个元素，LLVM IR 里是 1 条声明和 E 次调用；分清职责：Triton 一直降级到 LLVM IR，LLVM 负责链接、O3 和生成 PTX；说明按名字只链接用到的定义，O3 内联后没有 call；说明反射参数在生成 PTX 时选定默认的数值模式</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 编译器前置与逐元素调用、链接、内联；综合验收与复查</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请用约 60–90 秒回答面试官：Triton 3.7.1 编译的 kernel（手写，或由 PyTorch 2.13 的 Inductor 生成）和 PyTorch eager 相比，个别元素不一致：有的差最后一两位，有的在极小的数上一个得 0、一个不是 0。可能的来源有哪些？你会怎样排查和对齐？</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先按症状分流：极小的数一个得 0，查次正规数；差最后一两位，查快速档运算和数学库的版本。三类来源都能用写法或编译选项对齐。
+• [T#B#次正规数]：libdevice 默认把次正规数清零，eager 保留；传 enable_reflect_ftz=False 对齐，它只影响 libdevice 内部。
+• [T#B#快速档]：tl.exp、tl.sqrt、a / b 都是快速档，换成 libdevice.exp、tl.sqrt_rn、tl.div_rn。
+• [T#B#库的版本]：Triton 自带的 libdevice 与 CUDA 工具链那份多项式不同，erf、pow 会差约 1 ulp，可换用工具链的库。
+• [T#B#Inductor]：Inductor 默认只对 sqrt、exp 用精确写法；除法舍入、关闭 ftz、换用工具链 libdevice 这三个 eager_numerics 开关默认都关闭，要显式打开。
+[T#B,!c47f17#边界]：对齐有代价，精确档更慢，先确认是否真要逐位一致。跨后端默认值还可能相反：同一个 asin kernel 在 AMD 上默认保留次正规数。</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按症状分流：极小的数一个得 0 → 次正规数；差最后一两位 → 快速档或库的版本；说出 exp、sqrt、除法各自的精确写法；说出 enable_reflect_ftz=False 的作用，以及它只影响 libdevice 内部；说明 Inductor 的 eager_numerics 三个开关默认关闭，要显式打开；说明对齐有性能代价，并先确认是否需要逐位一致</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 四条实现路线与后端迁移；GPU 验收、观察与结课前答疑</t>
         </is>
       </c>
     </row>
